--- a/results/0916-all/汾渭谷地农业区/tech_selected_summary.xlsx
+++ b/results/0916-all/汾渭谷地农业区/tech_selected_summary.xlsx
@@ -307,229 +307,229 @@
     <t>周至县</t>
   </si>
   <si>
-    <t>县名</t>
-  </si>
-  <si>
-    <t>技术1</t>
-  </si>
-  <si>
-    <t>技术2</t>
-  </si>
-  <si>
-    <t>技术3</t>
-  </si>
-  <si>
-    <t>技术4</t>
-  </si>
-  <si>
-    <t>技术5</t>
-  </si>
-  <si>
-    <t>技术6</t>
-  </si>
-  <si>
-    <t>技术7</t>
-  </si>
-  <si>
-    <t>技术8</t>
-  </si>
-  <si>
-    <t>技术9</t>
-  </si>
-  <si>
-    <t>技术10</t>
-  </si>
-  <si>
-    <t>技术11</t>
-  </si>
-  <si>
-    <t>技术12</t>
-  </si>
-  <si>
-    <t>技术13</t>
-  </si>
-  <si>
-    <t>技术14</t>
-  </si>
-  <si>
-    <t>技术15</t>
-  </si>
-  <si>
-    <t>技术16</t>
-  </si>
-  <si>
-    <t>技术17</t>
-  </si>
-  <si>
-    <t>技术18</t>
-  </si>
-  <si>
-    <t>技术19</t>
-  </si>
-  <si>
-    <t>技术20</t>
-  </si>
-  <si>
-    <t>技术21</t>
-  </si>
-  <si>
-    <t>技术22</t>
-  </si>
-  <si>
-    <t>技术23</t>
-  </si>
-  <si>
-    <t>技术24</t>
-  </si>
-  <si>
-    <t>技术25</t>
-  </si>
-  <si>
-    <t>技术26</t>
-  </si>
-  <si>
-    <t>技术27</t>
-  </si>
-  <si>
-    <t>技术28</t>
-  </si>
-  <si>
-    <t>技术29</t>
-  </si>
-  <si>
-    <t>技术30</t>
-  </si>
-  <si>
-    <t>技术31</t>
-  </si>
-  <si>
-    <t>技术32</t>
-  </si>
-  <si>
-    <t>技术33</t>
-  </si>
-  <si>
-    <t>技术34</t>
-  </si>
-  <si>
-    <t>技术35</t>
-  </si>
-  <si>
-    <t>技术36</t>
-  </si>
-  <si>
-    <t>技术37</t>
-  </si>
-  <si>
-    <t>技术38</t>
-  </si>
-  <si>
-    <t>技术39</t>
-  </si>
-  <si>
-    <t>技术40</t>
-  </si>
-  <si>
-    <t>技术41</t>
-  </si>
-  <si>
-    <t>技术42</t>
-  </si>
-  <si>
-    <t>技术43</t>
-  </si>
-  <si>
-    <t>技术44</t>
-  </si>
-  <si>
-    <t>技术45</t>
-  </si>
-  <si>
-    <t>技术46</t>
-  </si>
-  <si>
-    <t>技术47</t>
-  </si>
-  <si>
-    <t>技术48</t>
-  </si>
-  <si>
-    <t>技术49</t>
-  </si>
-  <si>
-    <t>技术50</t>
-  </si>
-  <si>
-    <t>技术51</t>
-  </si>
-  <si>
-    <t>技术52</t>
-  </si>
-  <si>
-    <t>技术53</t>
-  </si>
-  <si>
-    <t>技术54</t>
-  </si>
-  <si>
-    <t>技术55</t>
-  </si>
-  <si>
-    <t>技术56</t>
-  </si>
-  <si>
-    <t>技术57</t>
-  </si>
-  <si>
-    <t>技术58</t>
-  </si>
-  <si>
-    <t>技术59</t>
-  </si>
-  <si>
-    <t>技术60</t>
-  </si>
-  <si>
-    <t>技术61</t>
-  </si>
-  <si>
-    <t>技术62</t>
-  </si>
-  <si>
-    <t>技术63</t>
-  </si>
-  <si>
-    <t>技术64</t>
-  </si>
-  <si>
-    <t>技术65</t>
-  </si>
-  <si>
-    <t>技术66</t>
-  </si>
-  <si>
-    <t>技术67</t>
-  </si>
-  <si>
-    <t>技术68</t>
-  </si>
-  <si>
-    <t>技术69</t>
-  </si>
-  <si>
-    <t>技术70</t>
-  </si>
-  <si>
-    <t>技术71</t>
-  </si>
-  <si>
-    <t>技术72</t>
-  </si>
-  <si>
-    <t>技术73</t>
-  </si>
-  <si>
-    <t>总经济成本</t>
+    <t>Counties</t>
+  </si>
+  <si>
+    <t>Tech1</t>
+  </si>
+  <si>
+    <t>Tech2</t>
+  </si>
+  <si>
+    <t>Tech3</t>
+  </si>
+  <si>
+    <t>Tech4</t>
+  </si>
+  <si>
+    <t>Tech5</t>
+  </si>
+  <si>
+    <t>Tech6</t>
+  </si>
+  <si>
+    <t>Tech7</t>
+  </si>
+  <si>
+    <t>Tech8</t>
+  </si>
+  <si>
+    <t>Tech9</t>
+  </si>
+  <si>
+    <t>Tech10</t>
+  </si>
+  <si>
+    <t>Tech11</t>
+  </si>
+  <si>
+    <t>Tech12</t>
+  </si>
+  <si>
+    <t>Tech13</t>
+  </si>
+  <si>
+    <t>Tech14</t>
+  </si>
+  <si>
+    <t>Tech15</t>
+  </si>
+  <si>
+    <t>Tech16</t>
+  </si>
+  <si>
+    <t>Tech17</t>
+  </si>
+  <si>
+    <t>Tech18</t>
+  </si>
+  <si>
+    <t>Tech19</t>
+  </si>
+  <si>
+    <t>Tech20</t>
+  </si>
+  <si>
+    <t>Tech21</t>
+  </si>
+  <si>
+    <t>Tech22</t>
+  </si>
+  <si>
+    <t>Tech23</t>
+  </si>
+  <si>
+    <t>Tech24</t>
+  </si>
+  <si>
+    <t>Tech25</t>
+  </si>
+  <si>
+    <t>Tech26</t>
+  </si>
+  <si>
+    <t>Tech27</t>
+  </si>
+  <si>
+    <t>Tech28</t>
+  </si>
+  <si>
+    <t>Tech29</t>
+  </si>
+  <si>
+    <t>Tech30</t>
+  </si>
+  <si>
+    <t>Tech31</t>
+  </si>
+  <si>
+    <t>Tech32</t>
+  </si>
+  <si>
+    <t>Tech33</t>
+  </si>
+  <si>
+    <t>Tech34</t>
+  </si>
+  <si>
+    <t>Tech35</t>
+  </si>
+  <si>
+    <t>Tech36</t>
+  </si>
+  <si>
+    <t>Tech37</t>
+  </si>
+  <si>
+    <t>Tech38</t>
+  </si>
+  <si>
+    <t>Tech39</t>
+  </si>
+  <si>
+    <t>Tech40</t>
+  </si>
+  <si>
+    <t>Tech41</t>
+  </si>
+  <si>
+    <t>Tech42</t>
+  </si>
+  <si>
+    <t>Tech43</t>
+  </si>
+  <si>
+    <t>Tech44</t>
+  </si>
+  <si>
+    <t>Tech45</t>
+  </si>
+  <si>
+    <t>Tech46</t>
+  </si>
+  <si>
+    <t>Tech47</t>
+  </si>
+  <si>
+    <t>Tech48</t>
+  </si>
+  <si>
+    <t>Tech49</t>
+  </si>
+  <si>
+    <t>Tech50</t>
+  </si>
+  <si>
+    <t>Tech51</t>
+  </si>
+  <si>
+    <t>Tech52</t>
+  </si>
+  <si>
+    <t>Tech53</t>
+  </si>
+  <si>
+    <t>Tech54</t>
+  </si>
+  <si>
+    <t>Tech55</t>
+  </si>
+  <si>
+    <t>Tech56</t>
+  </si>
+  <si>
+    <t>Tech57</t>
+  </si>
+  <si>
+    <t>Tech58</t>
+  </si>
+  <si>
+    <t>Tech59</t>
+  </si>
+  <si>
+    <t>Tech60</t>
+  </si>
+  <si>
+    <t>Tech61</t>
+  </si>
+  <si>
+    <t>Tech62</t>
+  </si>
+  <si>
+    <t>Tech63</t>
+  </si>
+  <si>
+    <t>Tech64</t>
+  </si>
+  <si>
+    <t>Tech65</t>
+  </si>
+  <si>
+    <t>Tech66</t>
+  </si>
+  <si>
+    <t>Tech67</t>
+  </si>
+  <si>
+    <t>Tech68</t>
+  </si>
+  <si>
+    <t>Tech69</t>
+  </si>
+  <si>
+    <t>Tech70</t>
+  </si>
+  <si>
+    <t>Tech71</t>
+  </si>
+  <si>
+    <t>Tech72</t>
+  </si>
+  <si>
+    <t>Tech73</t>
+  </si>
+  <si>
+    <t>Total economic cost</t>
   </si>
   <si>
     <t>Feed processing_dairy</t>
@@ -664,7 +664,7 @@
     <t>irrigation (drip irrigation)_vegetable</t>
   </si>
   <si>
-    <t>总经济成本: 55709674.02</t>
+    <t>55709674.02</t>
   </si>
   <si>
     <t>Probiotics_poultry</t>
@@ -700,16 +700,16 @@
     <t>irrigation (drip irrigation)_friut</t>
   </si>
   <si>
-    <t>总经济成本: 182824185.15</t>
-  </si>
-  <si>
-    <t>总经济成本: 0.00</t>
+    <t>182824185.15</t>
+  </si>
+  <si>
+    <t>0.00</t>
   </si>
   <si>
     <t>nitrification inhibitor_dairy</t>
   </si>
   <si>
-    <t>总经济成本: 56529290.15</t>
+    <t>56529290.15</t>
   </si>
   <si>
     <t>Optimized aeration_pig</t>
@@ -718,13 +718,13 @@
     <t>EEF(NI)_rice</t>
   </si>
   <si>
-    <t>总经济成本: 180672562.28</t>
+    <t>180672562.28</t>
   </si>
   <si>
     <t>irrigation (drip irrigation)_maize</t>
   </si>
   <si>
-    <t>总经济成本: 134704155.99</t>
+    <t>134704155.99</t>
   </si>
   <si>
     <t>Biochar_sheep &amp; goat</t>
@@ -736,7 +736,7 @@
     <t>nitrification inhibitor_poultry</t>
   </si>
   <si>
-    <t>总经济成本: 125630072.41</t>
+    <t>125630072.41</t>
   </si>
   <si>
     <t>Organic acid_sheep &amp; goat</t>
@@ -775,13 +775,13 @@
     <t>irrigation (water-saving irrigation)_rice</t>
   </si>
   <si>
-    <t>总经济成本: 377349519.75</t>
-  </si>
-  <si>
-    <t>总经济成本: 35597636.31</t>
-  </si>
-  <si>
-    <t>总经济成本: 159770223.13</t>
+    <t>377349519.75</t>
+  </si>
+  <si>
+    <t>35597636.31</t>
+  </si>
+  <si>
+    <t>159770223.13</t>
   </si>
   <si>
     <t>surface crust cover_dairy</t>
@@ -790,7 +790,7 @@
     <t>EEF(DI)_maize</t>
   </si>
   <si>
-    <t>总经济成本: 234100189.00</t>
+    <t>234100189.00</t>
   </si>
   <si>
     <t>surface crust cover_pig</t>
@@ -805,7 +805,7 @@
     <t>4R(Right type)_wheat</t>
   </si>
   <si>
-    <t>总经济成本: 579908790.72</t>
+    <t>579908790.72</t>
   </si>
   <si>
     <t>chemical amendments_dairy</t>
@@ -817,10 +817,10 @@
     <t>incorporation_beef cattle</t>
   </si>
   <si>
-    <t>总经济成本: 112922969.12</t>
-  </si>
-  <si>
-    <t>总经济成本: 44542064.71</t>
+    <t>112922969.12</t>
+  </si>
+  <si>
+    <t>44542064.71</t>
   </si>
   <si>
     <t>Organic acid_pig</t>
@@ -832,40 +832,40 @@
     <t>nitrification inhibitor_sheep&amp;goat</t>
   </si>
   <si>
-    <t>总经济成本: 196939552.47</t>
-  </si>
-  <si>
-    <t>总经济成本: 3723240.47</t>
+    <t>196939552.47</t>
+  </si>
+  <si>
+    <t>3723240.47</t>
   </si>
   <si>
     <t>compost（add)_vegetable</t>
   </si>
   <si>
-    <t>总经济成本: 20687922.22</t>
-  </si>
-  <si>
-    <t>总经济成本: 249670776.40</t>
-  </si>
-  <si>
-    <t>总经济成本: 71250638.26</t>
-  </si>
-  <si>
-    <t>总经济成本: 155190735.00</t>
-  </si>
-  <si>
-    <t>总经济成本: 4375782.71</t>
-  </si>
-  <si>
-    <t>总经济成本: 47389068.30</t>
-  </si>
-  <si>
-    <t>总经济成本: 891526.08</t>
+    <t>20687922.22</t>
+  </si>
+  <si>
+    <t>249670776.40</t>
+  </si>
+  <si>
+    <t>71250638.26</t>
+  </si>
+  <si>
+    <t>155190735.00</t>
+  </si>
+  <si>
+    <t>4375782.71</t>
+  </si>
+  <si>
+    <t>47389068.30</t>
+  </si>
+  <si>
+    <t>891526.08</t>
   </si>
   <si>
     <t>Feedstock adjustment_beef cattle</t>
   </si>
   <si>
-    <t>总经济成本: 15171088.86</t>
+    <t>15171088.86</t>
   </si>
   <si>
     <t>Decreasing grass maturity_beef cattle</t>
@@ -877,7 +877,7 @@
     <t>Plant-derived N substitution_maize</t>
   </si>
   <si>
-    <t>总经济成本: 427191263.80</t>
+    <t>427191263.80</t>
   </si>
   <si>
     <t>compost（mid）30%-70%_wheat</t>
@@ -886,37 +886,37 @@
     <t>biochar_maize</t>
   </si>
   <si>
-    <t>总经济成本: 449813212.22</t>
-  </si>
-  <si>
-    <t>总经济成本: 259913021.00</t>
-  </si>
-  <si>
-    <t>总经济成本: 789707694.03</t>
-  </si>
-  <si>
-    <t>总经济成本: 530986081.35</t>
+    <t>449813212.22</t>
+  </si>
+  <si>
+    <t>259913021.00</t>
+  </si>
+  <si>
+    <t>789707694.03</t>
+  </si>
+  <si>
+    <t>530986081.35</t>
   </si>
   <si>
     <t>residue rerention_maize</t>
   </si>
   <si>
-    <t>总经济成本: 206698936.13</t>
-  </si>
-  <si>
-    <t>总经济成本: 23802489.21</t>
+    <t>206698936.13</t>
+  </si>
+  <si>
+    <t>23802489.21</t>
   </si>
   <si>
     <t>4R(Right type)_rice</t>
   </si>
   <si>
-    <t>总经济成本: 314087761.74</t>
-  </si>
-  <si>
-    <t>总经济成本: 10295164.99</t>
-  </si>
-  <si>
-    <t>总经济成本: 303008590.05</t>
+    <t>314087761.74</t>
+  </si>
+  <si>
+    <t>10295164.99</t>
+  </si>
+  <si>
+    <t>303008590.05</t>
   </si>
   <si>
     <t>Oil_dairy</t>
@@ -925,55 +925,55 @@
     <t>Frequent removal_sheep&amp;goat</t>
   </si>
   <si>
-    <t>总经济成本: 113455271.77</t>
-  </si>
-  <si>
-    <t>总经济成本: 125369642.50</t>
-  </si>
-  <si>
-    <t>总经济成本: 29746620.15</t>
-  </si>
-  <si>
-    <t>总经济成本: 327424189.00</t>
+    <t>113455271.77</t>
+  </si>
+  <si>
+    <t>125369642.50</t>
+  </si>
+  <si>
+    <t>29746620.15</t>
+  </si>
+  <si>
+    <t>327424189.00</t>
   </si>
   <si>
     <t>manure（low）≤30%_vegetable</t>
   </si>
   <si>
-    <t>总经济成本: 37965163.39</t>
-  </si>
-  <si>
-    <t>总经济成本: 36020473.58</t>
+    <t>37965163.39</t>
+  </si>
+  <si>
+    <t>36020473.58</t>
   </si>
   <si>
     <t>Feedstock adjustment_dairy</t>
   </si>
   <si>
-    <t>总经济成本: 71403631.20</t>
-  </si>
-  <si>
-    <t>总经济成本: 282322852.83</t>
+    <t>71403631.20</t>
+  </si>
+  <si>
+    <t>282322852.83</t>
   </si>
   <si>
     <t>EEF(NI)_vegetable</t>
   </si>
   <si>
-    <t>总经济成本: 108694030.85</t>
-  </si>
-  <si>
-    <t>总经济成本: 41461880.73</t>
-  </si>
-  <si>
-    <t>总经济成本: 32335502.63</t>
-  </si>
-  <si>
-    <t>总经济成本: 54713677.43</t>
+    <t>108694030.85</t>
+  </si>
+  <si>
+    <t>41461880.73</t>
+  </si>
+  <si>
+    <t>32335502.63</t>
+  </si>
+  <si>
+    <t>54713677.43</t>
   </si>
   <si>
     <t>Urease Inhibitor_poultry</t>
   </si>
   <si>
-    <t>总经济成本: 306062556.95</t>
+    <t>306062556.95</t>
   </si>
   <si>
     <t>incorporation_dairy</t>
@@ -982,49 +982,49 @@
     <t>residue rerention_rice</t>
   </si>
   <si>
-    <t>总经济成本: 177840233.32</t>
-  </si>
-  <si>
-    <t>总经济成本: 10516119.29</t>
-  </si>
-  <si>
-    <t>总经济成本: 5059500.77</t>
-  </si>
-  <si>
-    <t>总经济成本: 5339442.71</t>
-  </si>
-  <si>
-    <t>总经济成本: 136029982.32</t>
-  </si>
-  <si>
-    <t>总经济成本: 102097725.50</t>
+    <t>177840233.32</t>
+  </si>
+  <si>
+    <t>10516119.29</t>
+  </si>
+  <si>
+    <t>5059500.77</t>
+  </si>
+  <si>
+    <t>5339442.71</t>
+  </si>
+  <si>
+    <t>136029982.32</t>
+  </si>
+  <si>
+    <t>102097725.50</t>
   </si>
   <si>
     <t>irrigation (water-saving irrigation)_vegetable</t>
   </si>
   <si>
-    <t>总经济成本: 87918874.48</t>
-  </si>
-  <si>
-    <t>总经济成本: 117541101.65</t>
+    <t>87918874.48</t>
+  </si>
+  <si>
+    <t>117541101.65</t>
   </si>
   <si>
     <t>rolller press_pig</t>
   </si>
   <si>
-    <t>总经济成本: 247463407.36</t>
-  </si>
-  <si>
-    <t>总经济成本: 112762567.25</t>
-  </si>
-  <si>
-    <t>总经济成本: 146327515.20</t>
-  </si>
-  <si>
-    <t>总经济成本: 10078095.96</t>
-  </si>
-  <si>
-    <t>总经济成本: 84892946.86</t>
+    <t>247463407.36</t>
+  </si>
+  <si>
+    <t>112762567.25</t>
+  </si>
+  <si>
+    <t>146327515.20</t>
+  </si>
+  <si>
+    <t>10078095.96</t>
+  </si>
+  <si>
+    <t>84892946.86</t>
   </si>
   <si>
     <t>Probiotics_pig</t>
@@ -1075,22 +1075,22 @@
     <t>irrigation (water-saving irrigation)_friut</t>
   </si>
   <si>
-    <t>总经济成本: 580920413.89</t>
-  </si>
-  <si>
-    <t>总经济成本: 31227087.28</t>
-  </si>
-  <si>
-    <t>总经济成本: 1862445.03</t>
+    <t>580920413.89</t>
+  </si>
+  <si>
+    <t>31227087.28</t>
+  </si>
+  <si>
+    <t>1862445.03</t>
   </si>
   <si>
     <t>artificial film cover_pig</t>
   </si>
   <si>
-    <t>总经济成本: 75394973.10</t>
-  </si>
-  <si>
-    <t>总经济成本: 125117202.37</t>
+    <t>75394973.10</t>
+  </si>
+  <si>
+    <t>125117202.37</t>
   </si>
 </sst>
 </file>
